--- a/Apple_DCF_Model.xlsx.xlsx
+++ b/Apple_DCF_Model.xlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c48c79e69e11cf1c/Desktop/New folder/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c48c79e69e11cf1c/Desktop/Apple-DCF-Valuation/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="848" documentId="8_{DC15C2AB-65BE-4B98-BA7F-3634F472553E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1F59D3F-C00F-4E26-A3B1-BC27F2918117}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{9FF9B8B7-5799-4F67-8300-65DED57386E7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9FF9B8B7-5799-4F67-8300-65DED57386E7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="8" r:id="rId1"/>

--- a/Apple_DCF_Model.xlsx.xlsx
+++ b/Apple_DCF_Model.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c48c79e69e11cf1c/Desktop/Apple-DCF-Valuation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="848" documentId="8_{DC15C2AB-65BE-4B98-BA7F-3634F472553E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1F59D3F-C00F-4E26-A3B1-BC27F2918117}"/>
+  <xr:revisionPtr revIDLastSave="854" documentId="8_{DC15C2AB-65BE-4B98-BA7F-3634F472553E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD87EFA0-20F8-420C-947B-A615F7D4E0B0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9FF9B8B7-5799-4F67-8300-65DED57386E7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{9FF9B8B7-5799-4F67-8300-65DED57386E7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="8" r:id="rId1"/>
@@ -7515,56 +7515,56 @@
         <v>121.28736086856776</v>
       </c>
       <c r="B42" s="65">
-        <v>0.12180000000000001</v>
+        <v>8.9300000000000004E-2</v>
       </c>
       <c r="C42" s="65">
-        <v>0.1318</v>
+        <v>9.9299999999999999E-2</v>
       </c>
       <c r="D42" s="66">
-        <v>0.14180000000000001</v>
+        <v>0.10929999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="102">
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="B43">
         <f t="dataTable" ref="B43:D45" dt2D="1" dtr="1" r1="M15" r2="M16"/>
-        <v>83.533247316208275</v>
+        <v>132.01003268818687</v>
       </c>
       <c r="C43">
-        <v>75.919377730992025</v>
+        <v>114.0336839675405</v>
       </c>
       <c r="D43" s="89">
-        <v>69.557209456459177</v>
+        <v>100.32428016363079</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="103">
-        <v>2.5000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="B44" s="54">
-        <v>87.173232770982864</v>
+        <v>141.98687208862921</v>
       </c>
       <c r="C44" s="54">
-        <v>78.870595244299324</v>
+        <v>121.28804474910341</v>
       </c>
       <c r="D44" s="89">
-        <v>71.991001385009099</v>
+        <v>105.81153167719167</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="104">
-        <v>0.03</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="B45" s="85">
-        <v>91.209730802530302</v>
+        <v>153.80106681143661</v>
       </c>
       <c r="C45" s="85">
-        <v>82.1117162461437</v>
+        <v>129.67061093992962</v>
       </c>
       <c r="D45" s="105">
-        <v>74.642484899296946</v>
+        <v>112.03730963941484</v>
       </c>
     </row>
   </sheetData>

--- a/Apple_DCF_Model.xlsx.xlsx
+++ b/Apple_DCF_Model.xlsx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c48c79e69e11cf1c/Desktop/Apple-DCF-Valuation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gargd\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="854" documentId="8_{DC15C2AB-65BE-4B98-BA7F-3634F472553E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD87EFA0-20F8-420C-947B-A615F7D4E0B0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6726DB1F-5647-4547-818A-9232E77437A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{9FF9B8B7-5799-4F67-8300-65DED57386E7}"/>
   </bookViews>
@@ -1564,10 +1564,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7515,7 +7511,7 @@
         <v>121.28736086856776</v>
       </c>
       <c r="B42" s="65">
-        <v>8.9300000000000004E-2</v>
+        <v>8.8300000000000003E-2</v>
       </c>
       <c r="C42" s="65">
         <v>9.9299999999999999E-2</v>
@@ -7530,7 +7526,7 @@
       </c>
       <c r="B43">
         <f t="dataTable" ref="B43:D45" dt2D="1" dtr="1" r1="M15" r2="M16"/>
-        <v>132.01003268818687</v>
+        <v>134.12020970253846</v>
       </c>
       <c r="C43">
         <v>114.0336839675405</v>
@@ -7544,7 +7540,7 @@
         <v>0.03</v>
       </c>
       <c r="B44" s="54">
-        <v>141.98687208862921</v>
+        <v>144.44744641710176</v>
       </c>
       <c r="C44" s="54">
         <v>121.28804474910341</v>
@@ -7558,7 +7554,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="B45" s="85">
-        <v>153.80106681143661</v>
+        <v>156.71225099556059</v>
       </c>
       <c r="C45" s="85">
         <v>129.67061093992962</v>
